--- a/artfynd/A 61830-2025 artfynd.xlsx
+++ b/artfynd/A 61830-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130241421</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130242384</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130242789</v>
       </c>
       <c r="B4" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130240753</v>
       </c>
       <c r="B5" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130242093</v>
       </c>
       <c r="B6" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130242046</v>
       </c>
       <c r="B7" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130240801</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>130240757</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>130241366</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130240844</v>
+        <v>130242951</v>
       </c>
       <c r="B11" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621960</v>
+        <v>621900</v>
       </c>
       <c r="R11" t="n">
-        <v>6896710</v>
+        <v>6896591</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1624,11 +1624,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd i hela området på gamla senvuxna granar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130242951</v>
+        <v>130240844</v>
       </c>
       <c r="B12" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621900</v>
+        <v>621960</v>
       </c>
       <c r="R12" t="n">
-        <v>6896591</v>
+        <v>6896710</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1726,6 +1721,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spridd i hela området på gamla senvuxna granar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130242561</v>
+        <v>130241920</v>
       </c>
       <c r="B14" t="n">
-        <v>79127</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621940</v>
+        <v>621881</v>
       </c>
       <c r="R14" t="n">
-        <v>6896779</v>
+        <v>6896799</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130241920</v>
+        <v>130242561</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>79212</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621881</v>
+        <v>621940</v>
       </c>
       <c r="R15" t="n">
-        <v>6896799</v>
+        <v>6896779</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>130242358</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>130241309</v>
       </c>
       <c r="B17" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>130241126</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>130242445</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>130242456</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130242286</v>
+        <v>130241305</v>
       </c>
       <c r="B21" t="n">
-        <v>91641</v>
+        <v>79212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621883</v>
+        <v>621931</v>
       </c>
       <c r="R21" t="n">
-        <v>6896861</v>
+        <v>6896774</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130241305</v>
+        <v>130242286</v>
       </c>
       <c r="B22" t="n">
-        <v>79127</v>
+        <v>91728</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621931</v>
+        <v>621883</v>
       </c>
       <c r="R22" t="n">
-        <v>6896774</v>
+        <v>6896861</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2725,7 +2725,7 @@
         <v>130241881</v>
       </c>
       <c r="B23" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 61830-2025 artfynd.xlsx
+++ b/artfynd/A 61830-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130241421</v>
+        <v>130240753</v>
       </c>
       <c r="B2" t="n">
-        <v>79801</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621931</v>
+        <v>621988</v>
       </c>
       <c r="R2" t="n">
-        <v>6896774</v>
+        <v>6896682</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130242384</v>
+        <v>130240844</v>
       </c>
       <c r="B3" t="n">
-        <v>91761</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621934</v>
+        <v>621960</v>
       </c>
       <c r="R3" t="n">
-        <v>6896882</v>
+        <v>6896710</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd i hela området på gamla senvuxna granar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130242789</v>
+        <v>130241305</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621902</v>
+        <v>621931</v>
       </c>
       <c r="R4" t="n">
-        <v>6896684</v>
+        <v>6896774</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130240753</v>
+        <v>130242046</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621988</v>
+        <v>621881</v>
       </c>
       <c r="R5" t="n">
-        <v>6896682</v>
+        <v>6896799</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1037,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spridd på många träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130242093</v>
+        <v>130242561</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621890</v>
+        <v>621940</v>
       </c>
       <c r="R6" t="n">
-        <v>6896840</v>
+        <v>6896779</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130242046</v>
+        <v>130242789</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621881</v>
+        <v>621902</v>
       </c>
       <c r="R7" t="n">
-        <v>6896799</v>
+        <v>6896684</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1231,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd på många träd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130240757</v>
+        <v>130242951</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621988</v>
+        <v>621900</v>
       </c>
       <c r="R8" t="n">
-        <v>6896682</v>
+        <v>6896591</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1362,7 +1367,7 @@
         <v>130240801</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130242951</v>
+        <v>130241881</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621900</v>
+        <v>621882</v>
       </c>
       <c r="R10" t="n">
-        <v>6896591</v>
+        <v>6896801</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130240844</v>
+        <v>130242093</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621960</v>
+        <v>621890</v>
       </c>
       <c r="R11" t="n">
-        <v>6896710</v>
+        <v>6896840</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1624,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd i hela området på gamla senvuxna granar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130241366</v>
+        <v>130242286</v>
       </c>
       <c r="B12" t="n">
-        <v>79830</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621931</v>
+        <v>621883</v>
       </c>
       <c r="R12" t="n">
-        <v>6896774</v>
+        <v>6896861</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1752,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130241448</v>
+        <v>130242384</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621897</v>
+        <v>621934</v>
       </c>
       <c r="R13" t="n">
-        <v>6896762</v>
+        <v>6896882</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1849,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130241920</v>
+        <v>130242456</v>
       </c>
       <c r="B14" t="n">
-        <v>98957</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621881</v>
+        <v>621951</v>
       </c>
       <c r="R14" t="n">
-        <v>6896799</v>
+        <v>6896876</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130242561</v>
+        <v>130242635</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621940</v>
+        <v>621911</v>
       </c>
       <c r="R15" t="n">
-        <v>6896779</v>
+        <v>6896722</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130242358</v>
+        <v>130241126</v>
       </c>
       <c r="B16" t="n">
-        <v>98957</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621970</v>
+        <v>621930</v>
       </c>
       <c r="R16" t="n">
-        <v>6896849</v>
+        <v>6896780</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>130241309</v>
       </c>
       <c r="B17" t="n">
-        <v>91725</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130241126</v>
+        <v>130242445</v>
       </c>
       <c r="B18" t="n">
-        <v>91725</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621930</v>
+        <v>621950</v>
       </c>
       <c r="R18" t="n">
-        <v>6896780</v>
+        <v>6896877</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2334,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130242445</v>
+        <v>130240757</v>
       </c>
       <c r="B19" t="n">
-        <v>91725</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621950</v>
+        <v>621988</v>
       </c>
       <c r="R19" t="n">
-        <v>6896877</v>
+        <v>6896682</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130242456</v>
+        <v>130241366</v>
       </c>
       <c r="B20" t="n">
-        <v>91761</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621951</v>
+        <v>621931</v>
       </c>
       <c r="R20" t="n">
-        <v>6896876</v>
+        <v>6896774</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130242286</v>
+        <v>130242761</v>
       </c>
       <c r="B21" t="n">
-        <v>91761</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621883</v>
+        <v>621894</v>
       </c>
       <c r="R21" t="n">
-        <v>6896861</v>
+        <v>6896710</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130241881</v>
+        <v>130263774</v>
       </c>
       <c r="B22" t="n">
-        <v>91761</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,37 +2636,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gästabodarna, Gästabodarna, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621882</v>
+        <v>621930</v>
       </c>
       <c r="R22" t="n">
-        <v>6896801</v>
+        <v>6896780</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2722,10 +2727,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130241305</v>
+        <v>130263775</v>
       </c>
       <c r="B23" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2738,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gästabodarna, Gästabodarna, Mpd</t>
+          <t>Vargberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621931</v>
+        <v>621907</v>
       </c>
       <c r="R23" t="n">
-        <v>6896774</v>
+        <v>6896799</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2822,7 +2832,7 @@
         <v>130263776</v>
       </c>
       <c r="B24" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,27 +2931,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130263775</v>
+        <v>130241448</v>
       </c>
       <c r="B25" t="n">
-        <v>57864</v>
+        <v>5199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2950,24 +2960,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Gästabodarna, Gästabodarna, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621907</v>
+        <v>621897</v>
       </c>
       <c r="R25" t="n">
-        <v>6896799</v>
+        <v>6896762</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3023,50 +3028,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130263774</v>
+        <v>130241920</v>
       </c>
       <c r="B26" t="n">
-        <v>57864</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vargberget, Mpd</t>
+          <t>Gästabodarna, Gästabodarna, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621930</v>
+        <v>621881</v>
       </c>
       <c r="R26" t="n">
-        <v>6896780</v>
+        <v>6896799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3122,6 +3122,200 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130242358</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gästabodarna, Gästabodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>621970</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6896849</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130241421</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gästabodarna, Gästabodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>621931</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6896774</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61830-2025 artfynd.xlsx
+++ b/artfynd/A 61830-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130240753</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130240844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241305</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242046</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242561</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242789</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242951</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130240801</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241881</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242093</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242286</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242384</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242456</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242635</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241126</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241309</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242445</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130240757</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241366</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242761</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2724,6 +2829,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263774</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263775</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130263776</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241448</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241920</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130242358</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,8 +3451,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130241421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>